--- a/record.xlsx
+++ b/record.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vijayamalla/Desktop/STC/B2CPP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\B2_CPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FA839AD-2D59-BF4D-8226-CA20F4EE1F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC37694F-C13B-44F5-8273-229B889C31E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" xr2:uid="{22C95809-E566-3540-A9BC-967C02D4B464}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{22C95809-E566-3540-A9BC-967C02D4B464}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>S.N.</t>
   </si>
@@ -68,24 +66,15 @@
     <t>Ashish Tamang</t>
   </si>
   <si>
-    <t>Bandana Thapa</t>
-  </si>
-  <si>
     <t>Bhishan Shrestha</t>
   </si>
   <si>
     <t>Binika Shrestha</t>
   </si>
   <si>
-    <t>Binod Raj Dhami</t>
-  </si>
-  <si>
     <t>Dev Narayan Mandal</t>
   </si>
   <si>
-    <t>Dipisha Katwal</t>
-  </si>
-  <si>
     <t>Gaurab Lama</t>
   </si>
   <si>
@@ -98,9 +87,6 @@
     <t>Kapil Shrestha</t>
   </si>
   <si>
-    <t>Khushi Rai</t>
-  </si>
-  <si>
     <t>Manisha Mainali</t>
   </si>
   <si>
@@ -110,9 +96,6 @@
     <t>Maria Shah Thakuri</t>
   </si>
   <si>
-    <t>Nirjala Ghimire</t>
-  </si>
-  <si>
     <t>Nischal Bade</t>
   </si>
   <si>
@@ -125,9 +108,6 @@
     <t>Nitesh Paudel</t>
   </si>
   <si>
-    <t>Nitika Thapa</t>
-  </si>
-  <si>
     <t>Opendra Giri</t>
   </si>
   <si>
@@ -186,18 +166,34 @@
   </si>
   <si>
     <t>Pre-Board Exam</t>
+  </si>
+  <si>
+    <t>Test-1</t>
+  </si>
+  <si>
+    <t>Attendance(if &gt; 80%)</t>
+  </si>
+  <si>
+    <t>Note: Incompleted, errored, copied task will not get specified marks.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -242,11 +238,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -260,22 +259,16 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -609,19 +602,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE5CE0CC-F099-9B47-B4C4-DC3AE70DD89A}">
-  <dimension ref="A1:G43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,22 +624,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -654,12 +655,18 @@
       <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -671,9 +678,13 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -683,12 +694,20 @@
       <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
       <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -698,12 +717,22 @@
       <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
@@ -712,9 +741,13 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
@@ -722,12 +755,22 @@
         <v>1</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -738,33 +781,47 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
       <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
@@ -773,53 +830,103 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
       <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
       <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
       <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
       <c r="B16" s="1" t="s">
         <v>16</v>
       </c>
@@ -828,50 +935,72 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
       <c r="B18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="3">
-        <v>1</v>
-      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="3">
         <v>1</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
       <c r="B20" s="1" t="s">
         <v>20</v>
       </c>
@@ -880,57 +1009,93 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
       <c r="B22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
       <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
       <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
       <c r="B24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="3">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
       <c r="B25" s="1" t="s">
         <v>25</v>
       </c>
@@ -939,9 +1104,13 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
       <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
@@ -951,12 +1120,20 @@
       <c r="D26" s="3">
         <v>1</v>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="E26" s="3">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
       <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
       <c r="B27" s="1" t="s">
         <v>27</v>
       </c>
@@ -966,45 +1143,89 @@
       <c r="D27" s="3">
         <v>1</v>
       </c>
-      <c r="E27" s="3"/>
+      <c r="E27" s="3">
+        <v>1</v>
+      </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
       <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
       <c r="B29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
       <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
       <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
       <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
@@ -1013,9 +1234,13 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
       <c r="B32" s="1" t="s">
         <v>32</v>
       </c>
@@ -1025,25 +1250,37 @@
       <c r="D32" s="3">
         <v>1</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
+      <c r="E32" s="3">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
       <c r="B33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="3">
-        <v>1</v>
-      </c>
+      <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
       <c r="B34" s="1" t="s">
         <v>34</v>
       </c>
@@ -1053,25 +1290,41 @@
       <c r="D34" s="3">
         <v>1</v>
       </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
+      <c r="E34" s="3">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="3">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3">
+        <v>1</v>
+      </c>
       <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="F35" s="3">
+        <v>1</v>
+      </c>
       <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
       <c r="B36" s="1" t="s">
         <v>36</v>
       </c>
@@ -1081,12 +1334,18 @@
       <c r="D36" s="3">
         <v>1</v>
       </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="3">
+        <v>1</v>
+      </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
       <c r="B37" s="1" t="s">
         <v>37</v>
       </c>
@@ -1095,91 +1354,31 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="3">
-        <v>1</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="3">
-        <v>1</v>
-      </c>
-      <c r="D40" s="3">
-        <v>1</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3">
-        <v>0</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="3">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="40" spans="1:9" ht="15.75">
+      <c r="B40" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:G43">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <mergeCells count="1">
+    <mergeCell ref="B40:I40"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C2:I37">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/record.xlsx
+++ b/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\B2_CPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2C7DD2-7908-46B2-BCFA-800372249A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB78EA91-7CE4-4EEB-9CF9-1ACB918D8F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -920,7 +920,9 @@
         <v>23</v>
       </c>
       <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
